--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.26998042233406</v>
+        <v>26.08865071076689</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.73552758954501</v>
+        <v>25.43491419971427</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.51703703217517</v>
+        <v>27.61403590322301</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.690889079328452</v>
+        <v>1.679098574189164</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58811.833780988</v>
+        <v>68987.85163415514</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.181857569623076</v>
+        <v>1.412856739348406</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1496.92</v>
+        <v>1366.653284107513</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2021.206666666667</v>
+        <v>2017.120019389637</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>2761.78</v>
+        <v>2627.426636830484</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26.73552758954501</v>
+        <v>25.43491419971427</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.73552758954501</v>
+        <v>25.43491419971427</v>
       </c>
     </row>
     <row r="15">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>21.69590190383995</v>
+        <v>20.55390481833024</v>
       </c>
       <c r="F11" t="n">
-        <v>17.15540622772998</v>
+        <v>16.25240509877783</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>28.51703703217517</v>
+        <v>27.61403590322301</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.97001497684741</v>
+        <v>18.02495120759367</v>
       </c>
       <c r="C2" t="n">
-        <v>22.35289772712861</v>
+        <v>21.28970098671816</v>
       </c>
       <c r="D2" t="n">
-        <v>25.7357804774098</v>
+        <v>24.55445076584264</v>
       </c>
       <c r="E2" t="n">
-        <v>29.11866322769101</v>
+        <v>27.81920054496712</v>
       </c>
       <c r="F2" t="n">
-        <v>32.5015459779722</v>
+        <v>31.08395032409159</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.73711494930954</v>
+        <v>18.7920511800558</v>
       </c>
       <c r="C3" t="n">
-        <v>23.11999769959073</v>
+        <v>22.05680095918028</v>
       </c>
       <c r="D3" t="n">
-        <v>26.50288044987193</v>
+        <v>25.32155073830477</v>
       </c>
       <c r="E3" t="n">
-        <v>29.88576320015314</v>
+        <v>28.58630051742925</v>
       </c>
       <c r="F3" t="n">
-        <v>33.26864595043433</v>
+        <v>31.85105029655372</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.50421492177166</v>
+        <v>19.55915115251793</v>
       </c>
       <c r="C4" t="n">
-        <v>23.88709767205286</v>
+        <v>22.82390093164241</v>
       </c>
       <c r="D4" t="n">
-        <v>27.26998042233406</v>
+        <v>26.08865071076689</v>
       </c>
       <c r="E4" t="n">
-        <v>30.65286317261526</v>
+        <v>29.35340048989137</v>
       </c>
       <c r="F4" t="n">
-        <v>34.03574592289645</v>
+        <v>32.61815026901584</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.27131489423379</v>
+        <v>20.32625112498005</v>
       </c>
       <c r="C5" t="n">
-        <v>24.65419764451499</v>
+        <v>23.59100090410454</v>
       </c>
       <c r="D5" t="n">
-        <v>28.03708039479618</v>
+        <v>26.85575068322902</v>
       </c>
       <c r="E5" t="n">
-        <v>31.41996314507739</v>
+        <v>30.1205004623535</v>
       </c>
       <c r="F5" t="n">
-        <v>34.80284589535858</v>
+        <v>33.38525024147798</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.03841486669592</v>
+        <v>21.09335109744218</v>
       </c>
       <c r="C6" t="n">
-        <v>25.42129761697712</v>
+        <v>24.35810087656667</v>
       </c>
       <c r="D6" t="n">
-        <v>28.80418036725831</v>
+        <v>27.62285065569115</v>
       </c>
       <c r="E6" t="n">
-        <v>32.18706311753952</v>
+        <v>30.88760043481563</v>
       </c>
       <c r="F6" t="n">
-        <v>35.56994586782071</v>
+        <v>34.1523502139401</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>27.5</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>28.18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>28.41</v>
+        <v>27.22</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.2</v>
+        <v>29.18</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>68987.85163415514</v>
+        <v>78344.9212529269</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.412856739348406</v>
+        <v>1.604487563591797</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.18</v>
+        <v>29.98</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>78344.9212529269</v>
+        <v>85983.34543151612</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.604487563591797</v>
+        <v>1.760920889504769</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.98</v>
+        <v>28.95</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>85983.34543151612</v>
+        <v>76148.87430158252</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.760920889504769</v>
+        <v>1.559512982391817</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>76148.87430158252</v>
+        <v>76148.87430158253</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>76148.87430158253</v>
+        <v>76148.87430158252</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.95</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>76148.87430158253</v>
+        <v>80540.96820427131</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.559512982391817</v>
+        <v>1.649462144791776</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.08865071076689</v>
+        <v>26.34949343319528</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.61403590322301</v>
+        <v>28.48351164465096</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>80540.96820427131</v>
+        <v>71405.00907716644</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.649462144791776</v>
+        <v>1.462359617065704</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>20.55390481833024</v>
+        <v>21.6535034022039</v>
       </c>
       <c r="F11" t="n">
-        <v>16.25240509877783</v>
+        <v>17.12188084020578</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>27.61403590322301</v>
+        <v>28.48351164465096</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.02495120759367</v>
+        <v>17.98216822331464</v>
       </c>
       <c r="C2" t="n">
-        <v>21.28970098671816</v>
+        <v>21.17293272886175</v>
       </c>
       <c r="D2" t="n">
-        <v>24.55445076584264</v>
+        <v>24.36369723440886</v>
       </c>
       <c r="E2" t="n">
-        <v>27.81920054496712</v>
+        <v>27.55446173995597</v>
       </c>
       <c r="F2" t="n">
-        <v>31.08395032409159</v>
+        <v>30.74522624550307</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.7920511800558</v>
+        <v>18.97506632270785</v>
       </c>
       <c r="C3" t="n">
-        <v>22.05680095918028</v>
+        <v>22.16583082825496</v>
       </c>
       <c r="D3" t="n">
-        <v>25.32155073830477</v>
+        <v>25.35659533380207</v>
       </c>
       <c r="E3" t="n">
-        <v>28.58630051742925</v>
+        <v>28.54735983934918</v>
       </c>
       <c r="F3" t="n">
-        <v>31.85105029655372</v>
+        <v>31.73812434489628</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.55915115251793</v>
+        <v>19.96796442210105</v>
       </c>
       <c r="C4" t="n">
-        <v>22.82390093164241</v>
+        <v>23.15872892764817</v>
       </c>
       <c r="D4" t="n">
-        <v>26.08865071076689</v>
+        <v>26.34949343319528</v>
       </c>
       <c r="E4" t="n">
-        <v>29.35340048989137</v>
+        <v>29.54025793874239</v>
       </c>
       <c r="F4" t="n">
-        <v>32.61815026901584</v>
+        <v>32.73102244428949</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.32625112498005</v>
+        <v>20.96086252149426</v>
       </c>
       <c r="C5" t="n">
-        <v>23.59100090410454</v>
+        <v>24.15162702704137</v>
       </c>
       <c r="D5" t="n">
-        <v>26.85575068322902</v>
+        <v>27.34239153258849</v>
       </c>
       <c r="E5" t="n">
-        <v>30.1205004623535</v>
+        <v>30.53315603813559</v>
       </c>
       <c r="F5" t="n">
-        <v>33.38525024147798</v>
+        <v>33.72392054368269</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.09335109744218</v>
+        <v>21.95376062088747</v>
       </c>
       <c r="C6" t="n">
-        <v>24.35810087656667</v>
+        <v>25.14452512643458</v>
       </c>
       <c r="D6" t="n">
-        <v>27.62285065569115</v>
+        <v>28.33528963198169</v>
       </c>
       <c r="E6" t="n">
-        <v>30.88760043481563</v>
+        <v>31.5260541375288</v>
       </c>
       <c r="F6" t="n">
-        <v>34.1523502139401</v>
+        <v>34.7168186430759</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>26.32</v>
+        <v>26.38</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>26.46</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>27.22</v>
+        <v>26.48</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.41</v>
+        <v>26.81</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>71405.00907716644</v>
+        <v>52225.63539617154</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.462359617065704</v>
+        <v>1.069570064705454</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52225.63539617154</v>
+        <v>52225.63539617155</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52225.63539617155</v>
+        <v>52225.63539617154</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.81</v>
+        <v>26.31</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52225.63539617154</v>
+        <v>48537.29430367252</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.069570064705454</v>
+        <v>0.9940336123284834</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -1268,7 +1268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1284,13 +1284,6 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
           <t>LR2 FFA forward curve is CONSTRUCTED (no market anchor) — built from the 12M TC + spot, not a Baltic / $MT / Worldscale series. Treat its dividend-strip contribution as indicative.</t>
         </is>
       </c>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.31</v>
+        <v>26.06</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>48537.29430367252</v>
+        <v>46693.123757423</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9940336123284834</v>
+        <v>0.9562653861399977</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.34949343319528</v>
+        <v>30.97229690780664</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25.43491419971427</v>
+        <v>30.34420427849516</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.48351164465096</v>
+        <v>32.4378463762001</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.679098574189164</v>
+        <v>1.674456931261281</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>46693.123757423</v>
+        <v>12732.7530731729</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9562653861399977</v>
+        <v>0.2627143302606264</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1366.653284107513</v>
+        <v>1372.653284107513</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2017.120019389637</v>
+        <v>2081.349684527703</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>196</v>
+        <v>196.4</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>110</v>
+        <v>254.9</v>
       </c>
     </row>
     <row r="7">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1089.6</v>
+        <v>-1081.8</v>
       </c>
     </row>
     <row r="8">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-5</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-360</v>
+        <v>-31.2</v>
       </c>
     </row>
     <row r="10">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>2627.426636830484</v>
+        <v>3134.55630196855</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25.43491419971427</v>
+        <v>30.34420427849516</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25.43491419971427</v>
+        <v>30.34420427849516</v>
       </c>
     </row>
     <row r="15">
@@ -833,13 +833,13 @@
         <v>22000</v>
       </c>
       <c r="D2" t="n">
-        <v>2.164672031643272</v>
+        <v>2.188333509983059</v>
       </c>
       <c r="E2" t="n">
-        <v>1.623504023732454</v>
+        <v>1.641250132487294</v>
       </c>
       <c r="F2" t="n">
-        <v>1.581694573465745</v>
+        <v>1.598983673774307</v>
       </c>
     </row>
     <row r="3">
@@ -855,13 +855,13 @@
         <v>30000</v>
       </c>
       <c r="D3" t="n">
-        <v>2.94915349340513</v>
+        <v>2.986458127601646</v>
       </c>
       <c r="E3" t="n">
-        <v>2.211865120053848</v>
+        <v>2.239843595701235</v>
       </c>
       <c r="F3" t="n">
-        <v>2.099409464225171</v>
+        <v>2.125965458094855</v>
       </c>
     </row>
     <row r="4">
@@ -877,13 +877,13 @@
         <v>28000</v>
       </c>
       <c r="D4" t="n">
-        <v>2.677995770752662</v>
+        <v>2.711889615984995</v>
       </c>
       <c r="E4" t="n">
-        <v>2.008496828064496</v>
+        <v>2.033917211988746</v>
       </c>
       <c r="F4" t="n">
-        <v>1.857286560357812</v>
+        <v>1.880793163286901</v>
       </c>
     </row>
     <row r="5">
@@ -899,13 +899,13 @@
         <v>19000</v>
       </c>
       <c r="D5" t="n">
-        <v>1.703362824237657</v>
+        <v>1.721908119131171</v>
       </c>
       <c r="E5" t="n">
-        <v>1.277522118178243</v>
+        <v>1.291431089348378</v>
       </c>
       <c r="F5" t="n">
-        <v>1.150920827187606</v>
+        <v>1.163451431845386</v>
       </c>
     </row>
     <row r="6">
@@ -921,13 +921,13 @@
         <v>18000</v>
       </c>
       <c r="D6" t="n">
-        <v>1.513211339484511</v>
+        <v>1.530051239895934</v>
       </c>
       <c r="E6" t="n">
-        <v>1.134908504613383</v>
+        <v>1.147538429921951</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9961096031318916</v>
+        <v>1.007194893122725</v>
       </c>
     </row>
     <row r="7">
@@ -943,13 +943,13 @@
         <v>23000</v>
       </c>
       <c r="D7" t="n">
-        <v>2.081960399261859</v>
+        <v>2.107327272083737</v>
       </c>
       <c r="E7" t="n">
-        <v>1.561470299446394</v>
+        <v>1.580495454062802</v>
       </c>
       <c r="F7" t="n">
-        <v>1.335209026891526</v>
+        <v>1.351477385111878</v>
       </c>
     </row>
     <row r="8">
@@ -965,13 +965,13 @@
         <v>26000</v>
       </c>
       <c r="D8" t="n">
-        <v>2.352265424673282</v>
+        <v>2.382748480941433</v>
       </c>
       <c r="E8" t="n">
-        <v>1.764199068504961</v>
+        <v>1.787061360706075</v>
       </c>
       <c r="F8" t="n">
-        <v>1.469712458252789</v>
+        <v>1.488758492383544</v>
       </c>
     </row>
     <row r="9">
@@ -987,13 +987,13 @@
         <v>18000</v>
       </c>
       <c r="D9" t="n">
-        <v>1.431352404344143</v>
+        <v>1.448192304755566</v>
       </c>
       <c r="E9" t="n">
-        <v>1.073514303258107</v>
+        <v>1.086144228566675</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8712882909326412</v>
+        <v>0.8815390216432715</v>
       </c>
     </row>
     <row r="10">
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>11.36163080444518</v>
+        <v>11.49816351926287</v>
       </c>
     </row>
     <row r="11">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>21.6535034022039</v>
+        <v>26.48175736155349</v>
       </c>
       <c r="F11" t="n">
-        <v>17.12188084020578</v>
+        <v>20.93968285693723</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>28.48351164465096</v>
+        <v>32.4378463762001</v>
       </c>
     </row>
     <row r="13">
@@ -1057,7 +1057,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.98216822331464</v>
+        <v>22.45925131804795</v>
       </c>
       <c r="C2" t="n">
-        <v>21.17293272886175</v>
+        <v>25.71060773107325</v>
       </c>
       <c r="D2" t="n">
-        <v>24.36369723440886</v>
+        <v>28.96196414409856</v>
       </c>
       <c r="E2" t="n">
-        <v>27.55446173995597</v>
+        <v>32.21332055712387</v>
       </c>
       <c r="F2" t="n">
-        <v>30.74522624550307</v>
+        <v>35.46467697014918</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.97506632270785</v>
+        <v>23.46441769990199</v>
       </c>
       <c r="C3" t="n">
-        <v>22.16583082825496</v>
+        <v>26.71577411292729</v>
       </c>
       <c r="D3" t="n">
-        <v>25.35659533380207</v>
+        <v>29.9671305259526</v>
       </c>
       <c r="E3" t="n">
-        <v>28.54735983934918</v>
+        <v>33.21848693897791</v>
       </c>
       <c r="F3" t="n">
-        <v>31.73812434489628</v>
+        <v>36.46984335200322</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.96796442210105</v>
+        <v>24.46958408175603</v>
       </c>
       <c r="C4" t="n">
-        <v>23.15872892764817</v>
+        <v>27.72094049478133</v>
       </c>
       <c r="D4" t="n">
-        <v>26.34949343319528</v>
+        <v>30.97229690780664</v>
       </c>
       <c r="E4" t="n">
-        <v>29.54025793874239</v>
+        <v>34.22365332083195</v>
       </c>
       <c r="F4" t="n">
-        <v>32.73102244428949</v>
+        <v>37.47500973385725</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.96086252149426</v>
+        <v>25.47475046361006</v>
       </c>
       <c r="C5" t="n">
-        <v>24.15162702704137</v>
+        <v>28.72610687663537</v>
       </c>
       <c r="D5" t="n">
-        <v>27.34239153258849</v>
+        <v>31.97746328966068</v>
       </c>
       <c r="E5" t="n">
-        <v>30.53315603813559</v>
+        <v>35.22881970268599</v>
       </c>
       <c r="F5" t="n">
-        <v>33.72392054368269</v>
+        <v>38.48017611571129</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.95376062088747</v>
+        <v>26.4799168454641</v>
       </c>
       <c r="C6" t="n">
-        <v>25.14452512643458</v>
+        <v>29.73127325848941</v>
       </c>
       <c r="D6" t="n">
-        <v>28.33528963198169</v>
+        <v>32.98262967151472</v>
       </c>
       <c r="E6" t="n">
-        <v>31.5260541375288</v>
+        <v>36.23398608454003</v>
       </c>
       <c r="F6" t="n">
-        <v>34.7168186430759</v>
+        <v>39.48534249756533</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>26.38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>26.46</v>
+        <v>31.08</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>26.48</v>
+        <v>31.11</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.06</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12732.7530731729</v>
+        <v>14186.06915756493</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2627143302606264</v>
+        <v>0.2927005366665678</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.25</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14186.06915756493</v>
+        <v>24799.08003572646</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2927005366665678</v>
+        <v>0.5116783200949993</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.7</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24799.08003572646</v>
+        <v>27402.8005138072</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5116783200949993</v>
+        <v>0.5654007694077152</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.06</v>
+        <v>29.48</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27402.8005138072</v>
+        <v>37673.03128845908</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5654007694077152</v>
+        <v>0.7773059861412075</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.48</v>
+        <v>28.86</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37673.03128845908</v>
+        <v>33188.84602065333</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7773059861412075</v>
+        <v>0.6847839901026405</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.86</v>
+        <v>29.425</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33188.84602065333</v>
+        <v>37275.24065986343</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6847839901026405</v>
+        <v>0.7690983897184318</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.425</v>
+        <v>28.45</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37275.24065986343</v>
+        <v>30223.4976983947</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7690983897184318</v>
+        <v>0.6236000894964915</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.97229690780664</v>
+        <v>30.93760899160785</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.34420427849516</v>
+        <v>30.30255258881536</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.4378463762001</v>
+        <v>32.41940726479032</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.674456931261281</v>
+        <v>1.673354290778231</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30223.4976983947</v>
+        <v>30419.48120188215</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6236000894964915</v>
+        <v>0.6287765334402506</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1372.653284107513</v>
+        <v>1364.403395742782</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2081.349684527703</v>
+        <v>2085.296953348511</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3134.55630196855</v>
+        <v>3130.253682424626</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.34420427849516</v>
+        <v>30.30255258881536</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.34420427849516</v>
+        <v>30.30255258881536</v>
       </c>
     </row>
     <row r="15">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>26.48175736155349</v>
+        <v>26.45843799813943</v>
       </c>
       <c r="F11" t="n">
-        <v>20.93968285693723</v>
+        <v>20.92124374552746</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>32.4378463762001</v>
+        <v>32.41940726479032</v>
       </c>
     </row>
     <row r="13">
@@ -1057,7 +1057,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.45925131804795</v>
+        <v>22.43150098508891</v>
       </c>
       <c r="C2" t="n">
-        <v>25.71060773107325</v>
+        <v>25.67938860649434</v>
       </c>
       <c r="D2" t="n">
-        <v>28.96196414409856</v>
+        <v>28.92727622789977</v>
       </c>
       <c r="E2" t="n">
-        <v>32.21332055712387</v>
+        <v>32.1751638493052</v>
       </c>
       <c r="F2" t="n">
-        <v>35.46467697014918</v>
+        <v>35.42305147071063</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.46441769990199</v>
+        <v>23.43666736694295</v>
       </c>
       <c r="C3" t="n">
-        <v>26.71577411292729</v>
+        <v>26.68455498834838</v>
       </c>
       <c r="D3" t="n">
-        <v>29.9671305259526</v>
+        <v>29.93244260975381</v>
       </c>
       <c r="E3" t="n">
-        <v>33.21848693897791</v>
+        <v>33.18033023115924</v>
       </c>
       <c r="F3" t="n">
-        <v>36.46984335200322</v>
+        <v>36.42821785256466</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.46958408175603</v>
+        <v>24.44183374879698</v>
       </c>
       <c r="C4" t="n">
-        <v>27.72094049478133</v>
+        <v>27.68972137020242</v>
       </c>
       <c r="D4" t="n">
-        <v>30.97229690780664</v>
+        <v>30.93760899160785</v>
       </c>
       <c r="E4" t="n">
-        <v>34.22365332083195</v>
+        <v>34.18549661301328</v>
       </c>
       <c r="F4" t="n">
-        <v>37.47500973385725</v>
+        <v>37.4333842344187</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.47475046361006</v>
+        <v>25.44700013065103</v>
       </c>
       <c r="C5" t="n">
-        <v>28.72610687663537</v>
+        <v>28.69488775205646</v>
       </c>
       <c r="D5" t="n">
-        <v>31.97746328966068</v>
+        <v>31.94277537346188</v>
       </c>
       <c r="E5" t="n">
-        <v>35.22881970268599</v>
+        <v>35.19066299486732</v>
       </c>
       <c r="F5" t="n">
-        <v>38.48017611571129</v>
+        <v>38.43855061627274</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.4799168454641</v>
+        <v>26.45216651250506</v>
       </c>
       <c r="C6" t="n">
-        <v>29.73127325848941</v>
+        <v>29.70005413391049</v>
       </c>
       <c r="D6" t="n">
-        <v>32.98262967151472</v>
+        <v>32.94794175531592</v>
       </c>
       <c r="E6" t="n">
-        <v>36.23398608454003</v>
+        <v>36.19582937672136</v>
       </c>
       <c r="F6" t="n">
-        <v>39.48534249756533</v>
+        <v>39.44371699812678</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>30.97</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>31.08</v>
+        <v>31.05</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>31.11</v>
+        <v>31.07</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30419.48120188215</v>
+        <v>30419.48120188216</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30419.48120188216</v>
+        <v>30419.48120188215</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.45</v>
+        <v>29.08</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30419.48120188216</v>
+        <v>34967.78359968375</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6287765334402506</v>
+        <v>0.7227908197375039</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.08</v>
+        <v>30.28</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34967.78359968375</v>
+        <v>43631.21673835346</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7227908197375039</v>
+        <v>0.9018656507798917</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43631.21673835346</v>
+        <v>43631.21673835347</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43631.21673835347</v>
+        <v>43631.21673835346</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.28</v>
+        <v>30.19</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43631.21673835347</v>
+        <v>42981.45925295327</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9018656507798917</v>
+        <v>0.888435038451713</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>42981.45925295327</v>
+        <v>42981.45925295326</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>42981.45925295326</v>
+        <v>42981.45925295327</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.19</v>
+        <v>29.49</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>42981.45925295326</v>
+        <v>37927.78992206257</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.888435038451713</v>
+        <v>0.7839747203436531</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.93760899160785</v>
+        <v>30.86564539483377</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.30255258881536</v>
+        <v>30.21852366130043</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.41940726479032</v>
+        <v>32.37559610641157</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.673354290778231</v>
+        <v>1.672517742122992</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37927.78992206257</v>
+        <v>38394.69061700383</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7839747203436531</v>
+        <v>0.7947137777882534</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1364.403395742782</v>
+        <v>1355.72320753049</v>
       </c>
     </row>
     <row r="3">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3130.253682424626</v>
+        <v>3121.573494212334</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.30255258881536</v>
+        <v>30.21852366130043</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.30255258881536</v>
+        <v>30.21852366130043</v>
       </c>
     </row>
     <row r="15">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>26.45843799813943</v>
+        <v>26.40303140607968</v>
       </c>
       <c r="F11" t="n">
-        <v>20.92124374552746</v>
+        <v>20.8774325871487</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>32.41940726479032</v>
+        <v>32.37559610641157</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.43150098508891</v>
+        <v>22.37393010766965</v>
       </c>
       <c r="C2" t="n">
-        <v>25.67938860649434</v>
+        <v>25.61462136939767</v>
       </c>
       <c r="D2" t="n">
-        <v>28.92727622789977</v>
+        <v>28.85531263112569</v>
       </c>
       <c r="E2" t="n">
-        <v>32.1751638493052</v>
+        <v>32.09600389285372</v>
       </c>
       <c r="F2" t="n">
-        <v>35.42305147071063</v>
+        <v>35.33669515458173</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.43666736694295</v>
+        <v>23.37909648952369</v>
       </c>
       <c r="C3" t="n">
-        <v>26.68455498834838</v>
+        <v>26.61978775125171</v>
       </c>
       <c r="D3" t="n">
-        <v>29.93244260975381</v>
+        <v>29.86047901297973</v>
       </c>
       <c r="E3" t="n">
-        <v>33.18033023115924</v>
+        <v>33.10117027470775</v>
       </c>
       <c r="F3" t="n">
-        <v>36.42821785256466</v>
+        <v>36.34186153643576</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.44183374879698</v>
+        <v>24.38426287137773</v>
       </c>
       <c r="C4" t="n">
-        <v>27.68972137020242</v>
+        <v>27.62495413310575</v>
       </c>
       <c r="D4" t="n">
-        <v>30.93760899160785</v>
+        <v>30.86564539483377</v>
       </c>
       <c r="E4" t="n">
-        <v>34.18549661301328</v>
+        <v>34.10633665656179</v>
       </c>
       <c r="F4" t="n">
-        <v>37.4333842344187</v>
+        <v>37.3470279182898</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.44700013065103</v>
+        <v>25.38942925323177</v>
       </c>
       <c r="C5" t="n">
-        <v>28.69488775205646</v>
+        <v>28.63012051495978</v>
       </c>
       <c r="D5" t="n">
-        <v>31.94277537346188</v>
+        <v>31.87081177668781</v>
       </c>
       <c r="E5" t="n">
-        <v>35.19066299486732</v>
+        <v>35.11150303841583</v>
       </c>
       <c r="F5" t="n">
-        <v>38.43855061627274</v>
+        <v>38.35219430014384</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.45216651250506</v>
+        <v>26.39459563508581</v>
       </c>
       <c r="C6" t="n">
-        <v>29.70005413391049</v>
+        <v>29.63528689681382</v>
       </c>
       <c r="D6" t="n">
-        <v>32.94794175531592</v>
+        <v>32.87597815854185</v>
       </c>
       <c r="E6" t="n">
-        <v>36.19582937672136</v>
+        <v>36.11666942026987</v>
       </c>
       <c r="F6" t="n">
-        <v>39.44371699812678</v>
+        <v>39.35736068199788</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>30.97</v>
+        <v>30.89</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>31.05</v>
+        <v>30.98</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>31.07</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.86564539483377</v>
+        <v>29.97814408611653</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.37559610641157</v>
+        <v>29.41725841068745</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22000</v>
+        <v>29250</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24750</v>
+        <v>29275</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.672517742122992</v>
+        <v>1.844281188865286</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38394.69061700383</v>
+        <v>37670.6460141237</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7947137777882534</v>
+        <v>0.9160342262142163</v>
       </c>
     </row>
   </sheetData>
@@ -827,19 +827,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22000</v>
+        <v>29300</v>
       </c>
       <c r="C2" t="n">
-        <v>22000</v>
+        <v>29300</v>
       </c>
       <c r="D2" t="n">
-        <v>2.188333509983059</v>
+        <v>2.180915043985963</v>
       </c>
       <c r="E2" t="n">
-        <v>1.641250132487294</v>
+        <v>1.635686282989472</v>
       </c>
       <c r="F2" t="n">
-        <v>1.598983673774307</v>
+        <v>1.593563107868931</v>
       </c>
     </row>
     <row r="3">
@@ -849,19 +849,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30000</v>
+        <v>29300</v>
       </c>
       <c r="C3" t="n">
-        <v>30000</v>
+        <v>29300</v>
       </c>
       <c r="D3" t="n">
-        <v>2.986458127601646</v>
+        <v>2.180915043985963</v>
       </c>
       <c r="E3" t="n">
-        <v>2.239843595701235</v>
+        <v>1.635686282989472</v>
       </c>
       <c r="F3" t="n">
-        <v>2.125965458094855</v>
+        <v>1.552524714042143</v>
       </c>
     </row>
     <row r="4">
@@ -871,19 +871,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28000</v>
+        <v>29250</v>
       </c>
       <c r="C4" t="n">
-        <v>28000</v>
+        <v>29250</v>
       </c>
       <c r="D4" t="n">
-        <v>2.711889615984995</v>
+        <v>1.947574443973862</v>
       </c>
       <c r="E4" t="n">
-        <v>2.033917211988746</v>
+        <v>1.460680832980397</v>
       </c>
       <c r="F4" t="n">
-        <v>1.880793163286901</v>
+        <v>1.350713051750774</v>
       </c>
     </row>
     <row r="5">
@@ -893,19 +893,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19000</v>
+        <v>29250</v>
       </c>
       <c r="C5" t="n">
-        <v>19000</v>
+        <v>29250</v>
       </c>
       <c r="D5" t="n">
-        <v>1.721908119131171</v>
+        <v>1.947574443973862</v>
       </c>
       <c r="E5" t="n">
-        <v>1.291431089348378</v>
+        <v>1.460680832980397</v>
       </c>
       <c r="F5" t="n">
-        <v>1.163451431845386</v>
+        <v>1.315928678360718</v>
       </c>
     </row>
     <row r="6">
@@ -915,19 +915,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="C6" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="D6" t="n">
-        <v>1.530051239895934</v>
+        <v>1.345015938589061</v>
       </c>
       <c r="E6" t="n">
-        <v>1.147538429921951</v>
+        <v>1.008761953941796</v>
       </c>
       <c r="F6" t="n">
-        <v>1.007194893122725</v>
+        <v>0.8853907301873826</v>
       </c>
     </row>
     <row r="7">
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23000</v>
+        <v>25000</v>
       </c>
       <c r="C7" t="n">
-        <v>23000</v>
+        <v>25000</v>
       </c>
       <c r="D7" t="n">
-        <v>2.107327272083737</v>
+        <v>1.345015938589061</v>
       </c>
       <c r="E7" t="n">
-        <v>1.580495454062802</v>
+        <v>1.008761953941796</v>
       </c>
       <c r="F7" t="n">
-        <v>1.351477385111878</v>
+        <v>0.8625896165718645</v>
       </c>
     </row>
     <row r="8">
@@ -959,19 +959,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26000</v>
+        <v>25000</v>
       </c>
       <c r="C8" t="n">
-        <v>26000</v>
+        <v>25000</v>
       </c>
       <c r="D8" t="n">
-        <v>2.382748480941433</v>
+        <v>1.345015938589061</v>
       </c>
       <c r="E8" t="n">
-        <v>1.787061360706075</v>
+        <v>1.008761953941796</v>
       </c>
       <c r="F8" t="n">
-        <v>1.488758492383544</v>
+        <v>0.8403756909224976</v>
       </c>
     </row>
     <row r="9">
@@ -981,19 +981,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="C9" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="D9" t="n">
-        <v>1.448192304755566</v>
+        <v>1.345015938589061</v>
       </c>
       <c r="E9" t="n">
-        <v>1.086144228566675</v>
+        <v>1.008761953941796</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8815390216432715</v>
+        <v>0.8187338316222675</v>
       </c>
     </row>
     <row r="10">
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>11.49816351926287</v>
+        <v>9.219819421326578</v>
       </c>
     </row>
     <row r="11">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>26.40303140607968</v>
+        <v>25.54306492105427</v>
       </c>
       <c r="F11" t="n">
-        <v>20.8774325871487</v>
+        <v>20.19743898936087</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>32.37559610641157</v>
+        <v>29.41725841068745</v>
       </c>
     </row>
     <row r="13">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24750</v>
+        <v>29275</v>
       </c>
     </row>
   </sheetData>
@@ -1058,7 +1058,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.37393010766965</v>
+        <v>21.75267919156759</v>
       </c>
       <c r="C2" t="n">
-        <v>25.61462136939767</v>
+        <v>24.9933704532956</v>
       </c>
       <c r="D2" t="n">
-        <v>28.85531263112569</v>
+        <v>28.23406171502362</v>
       </c>
       <c r="E2" t="n">
-        <v>32.09600389285372</v>
+        <v>31.47475297675165</v>
       </c>
       <c r="F2" t="n">
-        <v>35.33669515458173</v>
+        <v>34.71544423847966</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.37909648952369</v>
+        <v>22.62472037711404</v>
       </c>
       <c r="C3" t="n">
-        <v>26.61978775125171</v>
+        <v>25.86541163884206</v>
       </c>
       <c r="D3" t="n">
-        <v>29.86047901297973</v>
+        <v>29.10610290057008</v>
       </c>
       <c r="E3" t="n">
-        <v>33.10117027470775</v>
+        <v>32.3467941622981</v>
       </c>
       <c r="F3" t="n">
-        <v>36.34186153643576</v>
+        <v>35.58748542402611</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.38426287137773</v>
+        <v>23.49676156266049</v>
       </c>
       <c r="C4" t="n">
-        <v>27.62495413310575</v>
+        <v>26.73745282438851</v>
       </c>
       <c r="D4" t="n">
-        <v>30.86564539483377</v>
+        <v>29.97814408611653</v>
       </c>
       <c r="E4" t="n">
-        <v>34.10633665656179</v>
+        <v>33.21883534784456</v>
       </c>
       <c r="F4" t="n">
-        <v>37.3470279182898</v>
+        <v>36.45952660957257</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.38942925323177</v>
+        <v>24.36880274820695</v>
       </c>
       <c r="C5" t="n">
-        <v>28.63012051495978</v>
+        <v>27.60949400993496</v>
       </c>
       <c r="D5" t="n">
-        <v>31.87081177668781</v>
+        <v>30.85018527166298</v>
       </c>
       <c r="E5" t="n">
-        <v>35.11150303841583</v>
+        <v>34.09087653339101</v>
       </c>
       <c r="F5" t="n">
-        <v>38.35219430014384</v>
+        <v>37.33156779511902</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.39459563508581</v>
+        <v>25.2408439337534</v>
       </c>
       <c r="C6" t="n">
-        <v>29.63528689681382</v>
+        <v>28.48153519548141</v>
       </c>
       <c r="D6" t="n">
-        <v>32.87597815854185</v>
+        <v>31.72222645720944</v>
       </c>
       <c r="E6" t="n">
-        <v>36.11666942026987</v>
+        <v>34.96291771893746</v>
       </c>
       <c r="F6" t="n">
-        <v>39.35736068199788</v>
+        <v>38.20360898066548</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>30.89</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>30.98</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>31</v>
+        <v>30.09</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.49</v>
+        <v>28.97</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37670.6460141237</v>
+        <v>33992.33054742645</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9160342262142163</v>
+        <v>0.8265889095333048</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33992.33054742645</v>
+        <v>33992.33054742644</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33992.33054742644</v>
+        <v>33992.33054742645</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.97</v>
+        <v>30.08</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33992.33054742645</v>
+        <v>41844.11933210713</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8265889095333048</v>
+        <v>1.017520258602173</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.08</v>
+        <v>31.47</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41844.11933210713</v>
+        <v>51676.53952193251</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.017520258602173</v>
+        <v>1.256614470499225</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/trmd_fv_report.xlsx
+++ b/outputs/trmd_fv_report.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.47</v>
+        <v>32.62</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.97814408611653</v>
+        <v>32.14146860038935</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.21852366130043</v>
+        <v>32.30263883343863</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.41725841068745</v>
+        <v>31.76540472327437</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.844281188865286</v>
+        <v>1.842953835878171</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>51676.53952193251</v>
+        <v>43443.85177455599</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.256614470499225</v>
+        <v>1.078940263937</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1355.72320753049</v>
+        <v>1317.381092195365</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>342.2533333333334</v>
+        <v>330.82</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2085.296953348511</v>
+        <v>2310.973346482253</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>196.4</v>
+        <v>368.2</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254.9</v>
+        <v>342.7</v>
       </c>
     </row>
     <row r="7">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1081.8</v>
+        <v>-1076.2</v>
       </c>
     </row>
     <row r="8">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-31.2</v>
+        <v>-263.7</v>
       </c>
     </row>
     <row r="10">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3121.573494212334</v>
+        <v>3359.474438677617</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>103300000</v>
+        <v>104000000</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.21852366130043</v>
+        <v>32.30263883343863</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.21852366130043</v>
+        <v>32.30263883343863</v>
       </c>
     </row>
     <row r="15">
@@ -833,13 +833,13 @@
         <v>29300</v>
       </c>
       <c r="D2" t="n">
-        <v>2.180915043985963</v>
+        <v>2.273839220733173</v>
       </c>
       <c r="E2" t="n">
-        <v>1.635686282989472</v>
+        <v>1.70537941554988</v>
       </c>
       <c r="F2" t="n">
-        <v>1.593563107868931</v>
+        <v>1.661461461040362</v>
       </c>
     </row>
     <row r="3">
@@ -855,13 +855,13 @@
         <v>29300</v>
       </c>
       <c r="D3" t="n">
-        <v>2.180915043985963</v>
+        <v>2.273839220733173</v>
       </c>
       <c r="E3" t="n">
-        <v>1.635686282989472</v>
+        <v>1.70537941554988</v>
       </c>
       <c r="F3" t="n">
-        <v>1.552524714042143</v>
+        <v>1.618674508060892</v>
       </c>
     </row>
     <row r="4">
@@ -877,13 +877,13 @@
         <v>29250</v>
       </c>
       <c r="D4" t="n">
-        <v>1.947574443973862</v>
+        <v>2.041815095072115</v>
       </c>
       <c r="E4" t="n">
-        <v>1.460680832980397</v>
+        <v>1.531361321304086</v>
       </c>
       <c r="F4" t="n">
-        <v>1.350713051750774</v>
+        <v>1.416072338959417</v>
       </c>
     </row>
     <row r="5">
@@ -899,13 +899,13 @@
         <v>29250</v>
       </c>
       <c r="D5" t="n">
-        <v>1.947574443973862</v>
+        <v>2.041815095072115</v>
       </c>
       <c r="E5" t="n">
-        <v>1.460680832980397</v>
+        <v>1.531361321304086</v>
       </c>
       <c r="F5" t="n">
-        <v>1.315928678360718</v>
+        <v>1.379604793967645</v>
       </c>
     </row>
     <row r="6">
@@ -921,13 +921,13 @@
         <v>25000</v>
       </c>
       <c r="D6" t="n">
-        <v>1.345015938589061</v>
+        <v>1.421714844651442</v>
       </c>
       <c r="E6" t="n">
-        <v>1.008761953941796</v>
+        <v>1.066286133488582</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8853907301873826</v>
+        <v>0.9358797232876293</v>
       </c>
     </row>
     <row r="7">
@@ -943,13 +943,13 @@
         <v>25000</v>
       </c>
       <c r="D7" t="n">
-        <v>1.345015938589061</v>
+        <v>1.421714844651442</v>
       </c>
       <c r="E7" t="n">
-        <v>1.008761953941796</v>
+        <v>1.066286133488582</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8625896165718645</v>
+        <v>0.9117783868114449</v>
       </c>
     </row>
     <row r="8">
@@ -965,13 +965,13 @@
         <v>25000</v>
       </c>
       <c r="D8" t="n">
-        <v>1.345015938589061</v>
+        <v>1.421714844651442</v>
       </c>
       <c r="E8" t="n">
-        <v>1.008761953941796</v>
+        <v>1.066286133488582</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8403756909224976</v>
+        <v>0.8882977224210896</v>
       </c>
     </row>
     <row r="9">
@@ -987,13 +987,13 @@
         <v>25000</v>
       </c>
       <c r="D9" t="n">
-        <v>1.345015938589061</v>
+        <v>1.421714844651442</v>
       </c>
       <c r="E9" t="n">
-        <v>1.008761953941796</v>
+        <v>1.066286133488582</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8187338316222675</v>
+        <v>0.8654217461963978</v>
       </c>
     </row>
     <row r="10">
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9.219819421326578</v>
+        <v>9.677190680744879</v>
       </c>
     </row>
     <row r="11">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>25.54306492105427</v>
+        <v>27.93426857611351</v>
       </c>
       <c r="F11" t="n">
-        <v>20.19743898936087</v>
+        <v>22.08821404252949</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>29.41725841068745</v>
+        <v>31.76540472327437</v>
       </c>
     </row>
     <row r="13">
@@ -1058,7 +1058,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.75267919156759</v>
+        <v>23.56418576274073</v>
       </c>
       <c r="C2" t="n">
-        <v>24.9933704532956</v>
+        <v>26.94353569504453</v>
       </c>
       <c r="D2" t="n">
-        <v>28.23406171502362</v>
+        <v>30.32288562734832</v>
       </c>
       <c r="E2" t="n">
-        <v>31.47475297675165</v>
+        <v>33.70223555965212</v>
       </c>
       <c r="F2" t="n">
-        <v>34.71544423847966</v>
+        <v>37.08158549195591</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.62472037711404</v>
+        <v>24.47347724926124</v>
       </c>
       <c r="C3" t="n">
-        <v>25.86541163884206</v>
+        <v>27.85282718156504</v>
       </c>
       <c r="D3" t="n">
-        <v>29.10610290057008</v>
+        <v>31.23217711386884</v>
       </c>
       <c r="E3" t="n">
-        <v>32.3467941622981</v>
+        <v>34.61152704617264</v>
       </c>
       <c r="F3" t="n">
-        <v>35.58748542402611</v>
+        <v>37.99087697847641</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.49676156266049</v>
+        <v>25.38276873578176</v>
       </c>
       <c r="C4" t="n">
-        <v>26.73745282438851</v>
+        <v>28.76211866808556</v>
       </c>
       <c r="D4" t="n">
-        <v>29.97814408611653</v>
+        <v>32.14146860038935</v>
       </c>
       <c r="E4" t="n">
-        <v>33.21883534784456</v>
+        <v>35.52081853269316</v>
       </c>
       <c r="F4" t="n">
-        <v>36.45952660957257</v>
+        <v>38.90016846499693</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.36880274820695</v>
+        <v>26.29206022230227</v>
       </c>
       <c r="C5" t="n">
-        <v>27.60949400993496</v>
+        <v>29.67141015460607</v>
       </c>
       <c r="D5" t="n">
-        <v>30.85018527166298</v>
+        <v>33.05076008690986</v>
       </c>
       <c r="E5" t="n">
-        <v>34.09087653339101</v>
+        <v>36.43011001921366</v>
       </c>
       <c r="F5" t="n">
-        <v>37.33156779511902</v>
+        <v>39.80945995151744</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.2408439337534</v>
+        <v>27.20135170882279</v>
       </c>
       <c r="C6" t="n">
-        <v>28.48153519548141</v>
+        <v>30.58070164112658</v>
       </c>
       <c r="D6" t="n">
-        <v>31.72222645720944</v>
+        <v>33.96005157343038</v>
       </c>
       <c r="E6" t="n">
-        <v>34.96291771893746</v>
+        <v>37.33940150573418</v>
       </c>
       <c r="F6" t="n">
-        <v>38.20360898066548</v>
+        <v>40.71875143803796</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>32.17</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>30.07</v>
+        <v>32.24</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>30.09</v>
+        <v>32.26</v>
       </c>
     </row>
   </sheetData>
